--- a/OUTPUT/direct_Q79VI7_Corynebacterium_glutamicum_ATCC_13032.xlsx
+++ b/OUTPUT/direct_Q79VI7_Corynebacterium_glutamicum_ATCC_13032.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8472</v>
+        <v>0.8470611755297881</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8472</v>
+        <v>0.8470611755297881</v>
       </c>
     </row>
   </sheetData>
